--- a/mentor data/hadier 3 data3-talaria-adapted.xlsx
+++ b/mentor data/hadier 3 data3-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27705, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "exitScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27705, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "exitScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21812, "sourceLowPrice": 1.21571}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK2" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782553975334</v>
+        <v>1782575576862</v>
       </c>
       <c r="BM2" t="n">
         <v>1.21514</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27706, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "exitScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27706, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "exitScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07414, "sourceLowPrice": 1.07239}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK3" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782553975334</v>
+        <v>1782575576863</v>
       </c>
       <c r="BM3" t="n">
         <v>1.07424</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27839, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "exitScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27839, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "exitScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07742, "sourceLowPrice": 1.07522}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK4" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782553975334</v>
+        <v>1782575576863</v>
       </c>
       <c r="BM4" t="n">
         <v>1.07749</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27725, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27725, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.22905, "sourceLowPrice": 1.22852}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK5" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782553975334</v>
+        <v>1782575576864</v>
       </c>
       <c r="BM5" t="n">
         <v>1.22905</v>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27842, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27842, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08502, "sourceLowPrice": 1.08272}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK6" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782553975334</v>
+        <v>1782575576864</v>
       </c>
       <c r="BM6" t="n">
         <v>1.0846</v>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27827, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27827, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08758, "sourceLowPrice": 1.08487}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK7" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782553975334</v>
+        <v>1782575576865</v>
       </c>
       <c r="BM7" t="n">
         <v>1.08478</v>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27729, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "exitScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27729, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "exitScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08689, "sourceLowPrice": 1.08568}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK8" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782553975335</v>
+        <v>1782575576865</v>
       </c>
       <c r="BM8" t="n">
         <v>1.08565</v>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27847, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27847, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08805, "sourceLowPrice": 1.08469}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK9" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782553975335</v>
+        <v>1782575576866</v>
       </c>
       <c r="BM9" t="n">
         <v>1.08404</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27731, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "exitScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27731, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "exitScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23751, "sourceLowPrice": 1.23668}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK10" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782553975335</v>
+        <v>1782575576867</v>
       </c>
       <c r="BM10" t="n">
         <v>1.23668</v>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="DQ10" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR10" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS10" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27857, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "exitScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27857, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "exitScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23744, "sourceLowPrice": 1.23714}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6069,13 +6069,13 @@
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK11" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782553975335</v>
+        <v>1782575576867</v>
       </c>
       <c r="BM11" t="n">
         <v>1.23714</v>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27793, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "exitScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27793, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "exitScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2374, "sourceLowPrice": 1.2371}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6593,13 +6593,13 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK12" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782553975335</v>
+        <v>1782575576868</v>
       </c>
       <c r="BM12" t="n">
         <v>1.2371</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS12" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27701, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "exitScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27701, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "exitScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23926, "sourceLowPrice": 1.23703}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="BJ13" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK13" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782553975335</v>
+        <v>1782575576868</v>
       </c>
       <c r="BM13" t="n">
         <v>1.23701</v>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS13" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27923, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "exitScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27923, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "exitScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08926, "sourceLowPrice": 1.08883}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK14" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782553975336</v>
+        <v>1782575576869</v>
       </c>
       <c r="BM14" t="n">
         <v>1.08883</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS14" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27979, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "exitScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27979, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "exitScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23237, "sourceLowPrice": 1.22844}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK15" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782553975336</v>
+        <v>1782575576869</v>
       </c>
       <c r="BM15" t="n">
         <v>1.23286</v>
@@ -8373,12 +8373,12 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS15" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27972, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27972, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0924, "sourceLowPrice": 1.09155}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK16" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782553975336</v>
+        <v>1782575576870</v>
       </c>
       <c r="BM16" t="n">
         <v>1.09167</v>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS16" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27851, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "exitScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27851, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "exitScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09134, "sourceLowPrice": 1.09108}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="BJ17" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK17" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782553975336</v>
+        <v>1782575576870</v>
       </c>
       <c r="BM17" t="n">
         <v>1.09108</v>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS17" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27980, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "exitScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27980, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "exitScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09199, "sourceLowPrice": 1.0906}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9737,13 +9737,13 @@
         </is>
       </c>
       <c r="BJ18" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK18" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782553975336</v>
+        <v>1782575576870</v>
       </c>
       <c r="BM18" t="n">
         <v>1.09047</v>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR18" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27852, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27852, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07591, "sourceLowPrice": 1.07338}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10261,13 +10261,13 @@
         </is>
       </c>
       <c r="BJ19" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK19" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782553975336</v>
+        <v>1782575576871</v>
       </c>
       <c r="BM19" t="n">
         <v>1.07641</v>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR19" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS19" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27986, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "exitScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27986, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "exitScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20846, "sourceLowPrice": 1.20635}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="BJ20" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK20" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782553975337</v>
+        <v>1782575576871</v>
       </c>
       <c r="BM20" t="n">
         <v>1.20693</v>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR20" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS20" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27981, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27981, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20828, "sourceLowPrice": 1.20566}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="BJ21" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK21" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782553975337</v>
+        <v>1782575576871</v>
       </c>
       <c r="BM21" t="n">
         <v>1.20544</v>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR21" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS21" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27924, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "exitScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27924, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "exitScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21152, "sourceLowPrice": 1.21106}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="BJ22" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK22" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782553975337</v>
+        <v>1782575576872</v>
       </c>
       <c r="BM22" t="n">
         <v>1.21106</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="DQ22" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR22" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS22" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28019, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "exitScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28019, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "exitScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21218, "sourceLowPrice": 1.20956}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12357,13 +12357,13 @@
         </is>
       </c>
       <c r="BJ23" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK23" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782553975337</v>
+        <v>1782575576872</v>
       </c>
       <c r="BM23" t="n">
         <v>1.20935</v>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="DQ23" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR23" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS23" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28005, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "exitScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28005, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "exitScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06511, "sourceLowPrice": 1.06365}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12881,13 +12881,13 @@
         </is>
       </c>
       <c r="BJ24" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK24" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782553975337</v>
+        <v>1782575576873</v>
       </c>
       <c r="BM24" t="n">
         <v>1.0647</v>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="DQ24" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR24" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS24" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28094, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "exitScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28094, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "exitScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06821, "sourceLowPrice": 1.06712}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13405,13 +13405,13 @@
         </is>
       </c>
       <c r="BJ25" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK25" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782553975337</v>
+        <v>1782575576873</v>
       </c>
       <c r="BM25" t="n">
         <v>1.06769</v>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="DQ25" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR25" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28053, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "exitScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28053, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "exitScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20211, "sourceLowPrice": 1.19888}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13929,13 +13929,13 @@
         </is>
       </c>
       <c r="BJ26" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK26" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782553975338</v>
+        <v>1782575576874</v>
       </c>
       <c r="BM26" t="n">
         <v>1.20273</v>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="DQ26" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR26" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS26" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28095, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "exitScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28095, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "exitScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06939, "sourceLowPrice": 1.0685}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14453,13 +14453,13 @@
         </is>
       </c>
       <c r="BJ27" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK27" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782553975338</v>
+        <v>1782575576874</v>
       </c>
       <c r="BM27" t="n">
         <v>1.06845</v>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="DQ27" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR27" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS27" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28103, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "exitScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28103, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "exitScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20616, "sourceLowPrice": 1.20356}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14977,13 +14977,13 @@
         </is>
       </c>
       <c r="BJ28" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK28" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782553975338</v>
+        <v>1782575576875</v>
       </c>
       <c r="BM28" t="n">
         <v>1.20641</v>
@@ -15185,12 +15185,12 @@
       </c>
       <c r="DQ28" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR28" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS28" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28133, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28133, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19642, "sourceLowPrice": 1.19486}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="BJ29" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK29" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782553975338</v>
+        <v>1782575576875</v>
       </c>
       <c r="BM29" t="n">
         <v>1.19535</v>
@@ -15709,12 +15709,12 @@
       </c>
       <c r="DQ29" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR29" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28134, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "exitScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28134, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "exitScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05574, "sourceLowPrice": 1.05532}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16025,13 +16025,13 @@
         </is>
       </c>
       <c r="BJ30" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK30" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782553975338</v>
+        <v>1782575576875</v>
       </c>
       <c r="BM30" t="n">
         <v>1.05561</v>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="DQ30" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR30" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS30" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28166, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "exitScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28166, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "exitScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19601, "sourceLowPrice": 1.19346}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16549,13 +16549,13 @@
         </is>
       </c>
       <c r="BJ31" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK31" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782553975338</v>
+        <v>1782575576876</v>
       </c>
       <c r="BM31" t="n">
         <v>1.19641</v>
@@ -16757,12 +16757,12 @@
       </c>
       <c r="DQ31" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR31" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28200, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "exitScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28200, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "exitScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21247, "sourceLowPrice": 1.21008}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17073,13 +17073,13 @@
         </is>
       </c>
       <c r="BJ32" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK32" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782553975339</v>
+        <v>1782575576876</v>
       </c>
       <c r="BM32" t="n">
         <v>1.21064</v>
@@ -17281,12 +17281,12 @@
       </c>
       <c r="DQ32" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR32" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS32" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28167, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28167, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06083, "sourceLowPrice": 1.0604}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17597,13 +17597,13 @@
         </is>
       </c>
       <c r="BJ33" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BK33" t="n">
-        <v>964122</v>
+        <v>33</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782553975339</v>
+        <v>1782575576876</v>
       </c>
       <c r="BM33" t="n">
         <v>1.06058</v>
@@ -17805,12 +17805,12 @@
       </c>
       <c r="DQ33" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DR33" t="inlineStr">
         <is>
-          <t>journalAccount:964122</t>
+          <t>journalAccount:55</t>
         </is>
       </c>
       <c r="DS33" t="inlineStr">

--- a/mentor data/hadier 3 data3-talaria-adapted.xlsx
+++ b/mentor data/hadier 3 data3-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27705, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "exitScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21812, "sourceLowPrice": 1.21571}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27705, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "exitScreenshotUrl": "https://www.tradingview.com/x/v6v427Ir/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21812, "sourceLowPrice": 1.21571, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>33</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782575576862</v>
+        <v>1782578983479</v>
       </c>
       <c r="BM2" t="n">
         <v>1.21514</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27706, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "exitScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07414, "sourceLowPrice": 1.07239}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27706, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "exitScreenshotUrl": "https://www.tradingview.com/x/DCKA5R2t/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07414, "sourceLowPrice": 1.07239, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>33</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782575576863</v>
+        <v>1782578983479</v>
       </c>
       <c r="BM3" t="n">
         <v>1.07424</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27839, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "exitScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07742, "sourceLowPrice": 1.07522}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27839, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "exitScreenshotUrl": "https://www.tradingview.com/x/yJgA71Ah/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07742, "sourceLowPrice": 1.07522, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2407,7 +2407,7 @@
         <v>33</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782575576863</v>
+        <v>1782578983479</v>
       </c>
       <c r="BM4" t="n">
         <v>1.07749</v>
@@ -2588,11 +2588,11 @@
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27725, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.22905, "sourceLowPrice": 1.22852}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27725, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.22905, "sourceLowPrice": 1.22852, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2931,7 +2931,7 @@
         <v>33</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782575576864</v>
+        <v>1782578983479</v>
       </c>
       <c r="BM5" t="n">
         <v>1.22905</v>
@@ -3112,11 +3112,11 @@
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2023-01-17T09:58:00.000Z"}, {"type": "early_exit", "label": "Early Exit", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Closed before the planned target without a rule-based trigger.", "detected_at": "2023-01-17T09:58:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27842, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08502, "sourceLowPrice": 1.08272}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27842, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "exitScreenshotUrl": "https://www.tradingview.com/x/3GlE4sND/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08502, "sourceLowPrice": 1.08272, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3455,7 +3455,7 @@
         <v>33</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782575576864</v>
+        <v>1782578983479</v>
       </c>
       <c r="BM6" t="n">
         <v>1.0846</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27827, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08758, "sourceLowPrice": 1.08487}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27827, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZMnYzQVX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08758, "sourceLowPrice": 1.08487, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782575576865</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM7" t="n">
         <v>1.08478</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27729, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "exitScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08689, "sourceLowPrice": 1.08568}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27729, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "exitScreenshotUrl": "https://www.tradingview.com/x/x26RKmrz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08689, "sourceLowPrice": 1.08568, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4503,7 +4503,7 @@
         <v>33</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782575576865</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM8" t="n">
         <v>1.08565</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27847, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08805, "sourceLowPrice": 1.08469}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27847, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1h2V40s/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08805, "sourceLowPrice": 1.08469, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5027,7 +5027,7 @@
         <v>33</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782575576866</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM9" t="n">
         <v>1.08404</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27731, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "exitScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23751, "sourceLowPrice": 1.23668}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27731, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "exitScreenshotUrl": "https://www.tradingview.com/x/JSv07xH0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23751, "sourceLowPrice": 1.23668, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5551,7 +5551,7 @@
         <v>33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782575576867</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM10" t="n">
         <v>1.23668</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27857, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "exitScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23744, "sourceLowPrice": 1.23714}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27857, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "exitScreenshotUrl": "https://www.tradingview.com/x/A2UmmxDL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23744, "sourceLowPrice": 1.23714, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6075,7 +6075,7 @@
         <v>33</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782575576867</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM11" t="n">
         <v>1.23714</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27793, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "exitScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2374, "sourceLowPrice": 1.2371}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27793, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "exitScreenshotUrl": "https://www.tradingview.com/x/BgC1gZHO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2374, "sourceLowPrice": 1.2371, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6599,7 +6599,7 @@
         <v>33</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782575576868</v>
+        <v>1782578983480</v>
       </c>
       <c r="BM12" t="n">
         <v>1.2371</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27701, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "exitScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23926, "sourceLowPrice": 1.23703}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27701, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "exitScreenshotUrl": "https://www.tradingview.com/x/qPOcBT3B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23926, "sourceLowPrice": 1.23703, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7123,7 +7123,7 @@
         <v>33</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782575576868</v>
+        <v>1782578983481</v>
       </c>
       <c r="BM13" t="n">
         <v>1.23701</v>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27923, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "exitScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08926, "sourceLowPrice": 1.08883}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27923, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "exitScreenshotUrl": "https://www.tradingview.com/x/HsyvUGmK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08926, "sourceLowPrice": 1.08883, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7647,7 +7647,7 @@
         <v>33</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782575576869</v>
+        <v>1782578983481</v>
       </c>
       <c r="BM14" t="n">
         <v>1.08883</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27979, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "exitScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23237, "sourceLowPrice": 1.22844}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27979, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "exitScreenshotUrl": "https://www.tradingview.com/x/RoKsFQzg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.23237, "sourceLowPrice": 1.22844, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>33</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782575576869</v>
+        <v>1782578983481</v>
       </c>
       <c r="BM15" t="n">
         <v>1.23286</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27972, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0924, "sourceLowPrice": 1.09155}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27972, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/S3GA9EWQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0924, "sourceLowPrice": 1.09155, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8695,7 +8695,7 @@
         <v>33</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782575576870</v>
+        <v>1782578983481</v>
       </c>
       <c r="BM16" t="n">
         <v>1.09167</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27851, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "exitScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09134, "sourceLowPrice": 1.09108}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27851, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "exitScreenshotUrl": "https://www.tradingview.com/x/HOiuae9Z/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09134, "sourceLowPrice": 1.09108, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9219,7 +9219,7 @@
         <v>33</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782575576870</v>
+        <v>1782578983481</v>
       </c>
       <c r="BM17" t="n">
         <v>1.09108</v>
@@ -9400,11 +9400,11 @@
       </c>
       <c r="DL17" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="inlineStr">
         <is>
@@ -9478,12 +9478,12 @@
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2023-02-01T12:38:00.000Z"}, {"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2023-02-01T12:38:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27980, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "exitScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09199, "sourceLowPrice": 1.0906}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27980, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "exitScreenshotUrl": "https://www.tradingview.com/x/28VRhMwP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.09199, "sourceLowPrice": 1.0906, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9743,7 +9743,7 @@
         <v>33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782575576870</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM18" t="n">
         <v>1.09047</v>
@@ -9924,11 +9924,11 @@
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="EC18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED18" t="n">
         <v>2023</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="EF18" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27852, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07591, "sourceLowPrice": 1.07338}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27852, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Iap40HCt/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07591, "sourceLowPrice": 1.07338, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>33</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782575576871</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM19" t="n">
         <v>1.07641</v>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="DO19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.07641, "new": 1.0765, "at": 1675676460000}]</t>
         </is>
       </c>
       <c r="DP19" t="n">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27986, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "exitScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20846, "sourceLowPrice": 1.20635}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27986, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "exitScreenshotUrl": "https://www.tradingview.com/x/nqpQIRC2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20846, "sourceLowPrice": 1.20635, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>33</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782575576871</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM20" t="n">
         <v>1.20693</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27981, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20828, "sourceLowPrice": 1.20566}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27981, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7dr89Jy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20828, "sourceLowPrice": 1.20566, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11315,7 +11315,7 @@
         <v>33</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782575576871</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM21" t="n">
         <v>1.20544</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 27924, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "exitScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21152, "sourceLowPrice": 1.21106}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 27924, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "exitScreenshotUrl": "https://www.tradingview.com/x/Cg4jHYtz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21152, "sourceLowPrice": 1.21106, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11839,7 +11839,7 @@
         <v>33</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782575576872</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM22" t="n">
         <v>1.21106</v>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28019, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "exitScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21218, "sourceLowPrice": 1.20956}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28019, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "exitScreenshotUrl": "https://www.tradingview.com/x/aWm8fpFw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21218, "sourceLowPrice": 1.20956, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>33</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782575576872</v>
+        <v>1782578983482</v>
       </c>
       <c r="BM23" t="n">
         <v>1.20935</v>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28005, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "exitScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06511, "sourceLowPrice": 1.06365}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28005, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "exitScreenshotUrl": "https://www.tradingview.com/x/ntc3BOJk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06511, "sourceLowPrice": 1.06365, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12887,7 +12887,7 @@
         <v>33</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782575576873</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM24" t="n">
         <v>1.0647</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28094, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "exitScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06821, "sourceLowPrice": 1.06712}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28094, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "exitScreenshotUrl": "https://www.tradingview.com/x/34pwhzWW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06821, "sourceLowPrice": 1.06712, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13411,7 +13411,7 @@
         <v>33</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782575576873</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM25" t="n">
         <v>1.06769</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28053, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "exitScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20211, "sourceLowPrice": 1.19888}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28053, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "exitScreenshotUrl": "https://www.tradingview.com/x/9Y9ylu5r/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20211, "sourceLowPrice": 1.19888, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13935,7 +13935,7 @@
         <v>33</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782575576874</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM26" t="n">
         <v>1.20273</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28095, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "exitScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06939, "sourceLowPrice": 1.0685}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28095, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "exitScreenshotUrl": "https://www.tradingview.com/x/4VJhigPY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06939, "sourceLowPrice": 1.0685, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14459,7 +14459,7 @@
         <v>33</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782575576874</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM27" t="n">
         <v>1.06845</v>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28103, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "exitScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20616, "sourceLowPrice": 1.20356}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28103, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "exitScreenshotUrl": "https://www.tradingview.com/x/0nqeodat/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.20616, "sourceLowPrice": 1.20356, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14983,7 +14983,7 @@
         <v>33</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782575576875</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM28" t="n">
         <v>1.20641</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28133, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19642, "sourceLowPrice": 1.19486}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28133, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aCe6fMuZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19642, "sourceLowPrice": 1.19486, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15507,7 +15507,7 @@
         <v>33</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782575576875</v>
+        <v>1782578983483</v>
       </c>
       <c r="BM29" t="n">
         <v>1.19535</v>
@@ -15688,11 +15688,11 @@
       </c>
       <c r="DL29" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN29" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="EF29" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28134, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "exitScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05574, "sourceLowPrice": 1.05532}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28134, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "exitScreenshotUrl": "https://www.tradingview.com/x/PAqt8nmz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05574, "sourceLowPrice": 1.05532, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16031,7 +16031,7 @@
         <v>33</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782575576875</v>
+        <v>1782578983484</v>
       </c>
       <c r="BM30" t="n">
         <v>1.05561</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28166, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "exitScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19601, "sourceLowPrice": 1.19346}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28166, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "exitScreenshotUrl": "https://www.tradingview.com/x/YJA6XWda/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.19601, "sourceLowPrice": 1.19346, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16555,7 +16555,7 @@
         <v>33</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782575576876</v>
+        <v>1782578983484</v>
       </c>
       <c r="BM31" t="n">
         <v>1.19641</v>
@@ -16736,11 +16736,11 @@
       </c>
       <c r="DL31" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN31" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="EC31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED31" t="n">
         <v>2023</v>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="EF31" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28200, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "exitScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21247, "sourceLowPrice": 1.21008}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28200, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "exitScreenshotUrl": "https://www.tradingview.com/x/CMoIZKwV/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.21247, "sourceLowPrice": 1.21008, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17079,7 +17079,7 @@
         <v>33</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782575576876</v>
+        <v>1782578983484</v>
       </c>
       <c r="BM32" t="n">
         <v>1.21064</v>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28167, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06083, "sourceLowPrice": 1.0604}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28167, "mentorFile": "hadier 3 data3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Fbuo1UBX/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06083, "sourceLowPrice": 1.0604, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17603,7 +17603,7 @@
         <v>33</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782575576876</v>
+        <v>1782578983484</v>
       </c>
       <c r="BM33" t="n">
         <v>1.06058</v>
@@ -17784,11 +17784,11 @@
       </c>
       <c r="DL33" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 3 data3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN33" t="inlineStr">
         <is>
@@ -17862,12 +17862,12 @@
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2023-02-28T11:58:00.000Z"}, {"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2023-02-28T11:58:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
